--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -1403,45 +1403,45 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>晶圆 级自动台阶测试系统采购项目（重新招标）中标结果公示</t>
+          <t>ADC 自动缺陷检测系统 评标结果公示公告(1)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>待核验-缺少晶圆/衬底场景</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备</t>
+          <t>ADC 自动缺陷检测系统 评标结果公示公告(1)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>看到检测系统，但未看到晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆 级自动台阶测试系统采购项目（重新招标）中标结果公示；可见摘要：21小时前 中标结果 跨省</t>
+          <t>采购内容：ADC 自动缺陷检测系统 评标结果公示公告(1)；公告类型：结果公示；发布时间：2026-09-09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>必联网</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>结果公示</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1453,19 +1453,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-440599850-4.html</t>
+          <t>https://www.ebnew.com/businessShow/709843899.html</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-09-13T12:11:16</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告-0692-2640XM075270/04</t>
+          <t>晶圆 级自动台阶测试系统采购项目（重新招标）中标结果公示</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1485,14 +1485,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告-0692-2640XM075270/04；可见摘要：2026-09-07 中标结果 江苏</t>
+          <t>项目：晶圆 级自动台阶测试系统采购项目（重新招标）中标结果公示；可见摘要：21小时前 中标结果 跨省</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1508,14 +1508,14 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-440692963-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-440599850-4.html</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告</t>
+          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告-0692-2640XM075270/04</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告；可见摘要：2026-09-07 招标公告 广东</t>
+          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告-0692-2640XM075270/04；可见摘要：2026-09-07 中标结果 江苏</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-440696474-1.html</t>
+          <t>https://www.bidcenter.com.cn/news-440692963-4.html</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1589,27 +1589,27 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>全自动 晶圆 量测 设备评标结果公示公告(1)-0613-264028014245</t>
+          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：全自动 晶圆 量测 设备评标结果公示公告(1)-0613-264028014245；可见摘要：2026-09-07 中标结果 上海</t>
+          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台撤项公告；可见摘要：2026-09-07 招标公告 广东</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1627,19 +1627,19 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-440565406-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-440696474-1.html</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 量测设备评标结果公示公告</t>
+          <t>全自动 晶圆 量测 设备评标结果公示公告(1)-0613-264028014245</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 量测设备评标结果公示公告；可见摘要：2026-09-07 中标结果 上海</t>
+          <t>项目：全自动 晶圆 量测 设备评标结果公示公告(1)-0613-264028014245；可见摘要：2026-09-07 中标结果 上海</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-440565704-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-440565406-4.html</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1713,27 +1713,27 @@
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购中标结...</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 量测设备评标结果公示公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学量测</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购中标结...</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>成像，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>采购内容：北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购中标结...；发布时间：2026-09-07</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 量测设备评标结果公示公告；可见摘要：2026-09-07 中标结果 上海</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1746,10 +1746,14 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>已出结果</t>
@@ -1759,46 +1763,42 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709821095.html</t>
+          <t>https://www.bidcenter.com.cn/news-440565704-4.html</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:14:53</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购中标结...</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>晶圆/衬底光学量测</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>存储器测试系统</t>
+          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购中标结...</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>LPD，且公告具有半导体产业链语境</t>
+          <t>成像，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>采购内容：存储器测试系统；数量：1台；范围：_x0001_ 招标公告 存储器测试系统项目已具备招标条件；采购方：成都华微电子科技股份有限公司；公告类型：招标公告；发布时间：2026-09-07</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司</t>
-        </is>
-      </c>
+          <t>采购内容：北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购中标结...；发布时间：2026-09-07</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1808,36 +1808,32 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>招标公告</t>
-        </is>
-      </c>
+          <t>必联网</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/867829.jhtml</t>
+          <t>https://www.ebnew.com/businessShow/709821095.html</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T12:13:54</t>
+          <t>2026-09-10T12:14:53</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>检测仪采购</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1847,33 +1843,41 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测仪采购 [招标公告] 检测仪采购 发布时间：2026-09-04 招标信息？？招标单位电解铝项目名称检测仪？？招标联系人无手机无？？联系电话无联系邮件zhaobiao... 信息属性 所属行业： 半导体分立器件;温度仪表 ;建筑陶瓷 ;气体检测仪;集成电路;其他电子产品 所属地区： 山东省</t>
+          <t>存储器测试系统</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测仪，且公告具有半导体产业链语境</t>
+          <t>LPD，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>采购内容：检测仪采购 [招标公告] 检测仪采购 发布时间：2026-09-04 招标信息？？招标单位电解铝项目名称检测仪？？招标联系人无手机无？？联系电话无联系邮件zhaobiao... 信息属性 所属行业： 半导体分立器件;温度仪表 ;建筑陶瓷 ;气体检测仪;集成电路;其他电子产品 所属地区： 山东省；发布时间：2026-09-04</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>采购内容：存储器测试系统；数量：1台；范围：_x0001_ 招标公告 存储器测试系统项目已具备招标条件；采购方：成都华微电子科技股份有限公司；公告类型：招标公告；发布时间：2026-09-07</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>机电产品招标投标电子交易平台</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>中招联合</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>进行中/未知</t>
@@ -1883,19 +1887,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.chinabidding.com/bidDetail/263328491.html</t>
+          <t>https://www.365trade.com.cn/zhwzb/867829.jhtml</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05T12:10:27</t>
+          <t>2026-09-08T12:13:54</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目谈判采购公告</t>
+          <t>检测仪采购</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,17 +1909,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目谈判</t>
+          <t>检测仪采购 [招标公告] 检测仪采购 发布时间：2026-09-04 招标信息？？招标单位电解铝项目名称检测仪？？招标联系人无手机无？？联系电话无联系邮件zhaobiao... 信息属性 所属行业： 半导体分立器件;温度仪表 ;建筑陶瓷 ;气体检测仪;集成电路;其他电子产品 所属地区： 山东省</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告具有半导体产业链语境</t>
+          <t>检测仪，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目谈判；公告类型：采购公告；发布时间：2026-09-04</t>
+          <t>采购内容：检测仪采购 [招标公告] 检测仪采购 发布时间：2026-09-04 招标信息？？招标单位电解铝项目名称检测仪？？招标联系人无手机无？？联系电话无联系邮件zhaobiao... 信息属性 所属行业： 半导体分立器件;温度仪表 ;建筑陶瓷 ;气体检测仪;集成电路;其他电子产品 所属地区： 山东省；发布时间：2026-09-04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1928,14 +1932,10 @@
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>华润守正</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>采购公告</t>
-        </is>
-      </c>
+          <t>机电产品招标投标电子交易平台</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>进行中/未知</t>
@@ -1945,19 +1945,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_cggg/2026-09-04/2815492.html</t>
+          <t>https://www.chinabidding.com/bidDetail/263328491.html</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T12:11:01</t>
+          <t>2026-09-05T12:10:27</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目变更公告</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目谈判采购公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目谈判</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目；公告类型：变更公告；发布时间：2026-09-04</t>
+          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目谈判；公告类型：采购公告；发布时间：2026-09-04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -1995,19 +1995,19 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>变更公告</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_bggg/2026-09-04/2815334.html</t>
+          <t>https://www.szecp.com.cn/first_cggg/2026-09-04/2815492.html</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2019,89 +2019,89 @@
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所 自动光学检测系统采购项目</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目变更公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>TED，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所 自动光学检测系统采购项目；可见摘要：2026-09-03 招标公告 北京</t>
+          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目；公告类型：变更公告；发布时间：2026-09-04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>华润守正</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>变更公告</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-440148854-1.html</t>
+          <t>https://www.szecp.com.cn/first_bggg/2026-09-04/2815334.html</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-09-06T12:11:01</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>协同研制平台项目公告</t>
+          <t>中国科学院微电子研究所 自动光学检测系统采购项目</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>协同研制平台项目公告 [招标公告] 协同研制平台项目公告 发布时间：2026-09-03 协同研制平台招标公告*.招标条件本招标项目协同研制平台招标人为中国航空工业集团公司北京长城计量... 信息属性 所属行业： 实验室仪器;集成电路 所属地区： 北京市</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>计量，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>采购内容：协同研制平台项目公告 [招标公告] 协同研制平台项目公告 发布时间：2026-09-03 协同研制平台招标公告*.招标条件本招标项目协同研制平台招标人为中国航空工业集团公司北京长城计量... 信息属性 所属行业： 实验室仪器;集成电路 所属地区： 北京市；公告类型：公告；发布时间：2026-09-03</t>
+          <t>项目：中国科学院微电子研究所 自动光学检测系统采购项目；可见摘要：2026-09-03 招标公告 北京</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2114,12 +2114,12 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>机电产品招标投标电子交易平台</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2131,39 +2131,39 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.chinabidding.com/bidDetail/263326486.html</t>
+          <t>https://www.bidcenter.com.cn/news-440148854-1.html</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04T12:15:34</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>全自动晶圆 量测 机国际招标公告(1)</t>
+          <t>协同研制平台项目公告</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>待核验-采购对象不明确</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>晶圆 量测 机国际招标公告(1)</t>
+          <t>协同研制平台项目公告 [招标公告] 协同研制平台项目公告 发布时间：2026-09-03 协同研制平台招标公告*.招标条件本招标项目协同研制平台招标人为中国航空工业集团公司北京长城计量... 信息属性 所属行业： 实验室仪器;集成电路 所属地区： 北京市</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>看到量测，但未确认采购对象为设备/系统/仪器</t>
+          <t>计量，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆 量测 机国际招标公告(1)；公告类型：招标公告；发布时间：2026-09-03</t>
+          <t>采购内容：协同研制平台项目公告 [招标公告] 协同研制平台项目公告 发布时间：2026-09-03 协同研制平台招标公告*.招标条件本招标项目协同研制平台招标人为中国航空工业集团公司北京长城计量... 信息属性 所属行业： 实验室仪器;集成电路 所属地区： 北京市；公告类型：公告；发布时间：2026-09-03</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.chinabidding.com/bidDetail/263326902.html</t>
+          <t>https://www.chinabidding.com/bidDetail/263326486.html</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -2205,27 +2205,27 @@
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目最...</t>
+          <t>全自动晶圆 量测 机国际招标公告(1)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>待核验-设备功能不完整</t>
+          <t>待核验-采购对象不明确</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目最...</t>
+          <t>晶圆 量测 机国际招标公告(1)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
+          <t>看到量测，但未确认采购对象为设备/系统/仪器</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>采购内容：麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目最...；发布时间：2026-09-03</t>
+          <t>采购内容：晶圆 量测 机国际招标公告(1)；公告类型：招标公告；发布时间：2026-09-03</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -2238,10 +2238,14 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>机电产品招标投标电子交易平台</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
           <t>进行中/未知</t>
@@ -2251,7 +2255,7 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709769846.html</t>
+          <t>https://www.chinabidding.com/bidDetail/263326902.html</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2263,27 +2267,27 @@
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>全自动 晶圆 量测 机国际招标公告(1)</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目最...</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>待核验-采购对象不明确</t>
+          <t>待核验-设备功能不完整</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>晶圆 量测 机国际招标公告(1)</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目最...</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>看到量测，但未确认采购对象为设备/系统/仪器</t>
+          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆 量测 机国际招标公告(1)；公告类型：招标公告；发布时间：2026-09-03</t>
+          <t>采购内容：麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目最...；发布时间：2026-09-03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -2299,11 +2303,7 @@
           <t>必联网</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>招标公告</t>
-        </is>
-      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>进行中/未知</t>
@@ -2313,7 +2313,7 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709778343.html</t>
+          <t>https://www.ebnew.com/businessShow/709769846.html</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -2325,27 +2325,27 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>无锡华润微电子有限公司无锡华润上华科技BPWB01机台二次配项目谈判采购公告</t>
+          <t>全自动 晶圆 量测 机国际招标公告(1)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>待核验-采购对象不明确</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>无锡华润微电子有限公司无锡华润上华科技BPWB01机台二次配项目谈判</t>
+          <t>晶圆 量测 机国际招标公告(1)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告具有半导体产业链语境</t>
+          <t>看到量测，但未确认采购对象为设备/系统/仪器</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>采购内容：无锡华润微电子有限公司无锡华润上华科技BPWB01机台二次配项目谈判；公告类型：采购公告；发布时间：2026-09-03</t>
+          <t>采购内容：晶圆 量测 机国际招标公告(1)；公告类型：招标公告；发布时间：2026-09-03</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -2358,12 +2358,12 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>华润守正</t>
+          <t>必联网</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2375,19 +2375,19 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_cggg/2026-09-03/2811720.html</t>
+          <t>https://www.ebnew.com/businessShow/709778343.html</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T12:10:52</t>
+          <t>2026-09-04T12:15:34</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司6A新购AOI缺陷检测设备中标结果公告</t>
+          <t>无锡华润微电子有限公司无锡华润上华科技BPWB01机台二次配项目谈判采购公告</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2397,24 +2397,24 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>AOI缺陷检测设备</t>
+          <t>无锡华润微电子有限公司无锡华润上华科技BPWB01机台二次配项目谈判</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>检测设备，且公告具有半导体产业链语境</t>
+          <t>TED，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>采购内容：AOI缺陷检测设备；公告类型：结果公告；发布时间：2026-09-02</t>
+          <t>采购内容：无锡华润微电子有限公司无锡华润上华科技BPWB01机台二次配项目谈判；公告类型：采购公告；发布时间：2026-09-03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2425,19 +2425,19 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_zbgg1/2026-07-21/2811085.html</t>
+          <t>https://www.szecp.com.cn/first_cggg/2026-09-03/2811720.html</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -2449,45 +2449,45 @@
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片外观自动检测机采购项目成交候选人公示</t>
+          <t>无锡华润上华科技有限公司6A新购AOI缺陷检测设备中标结果公告</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>AOI缺陷检测设备</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片外观自动检测机采购项目成交候选人公示；可见摘要：3小时前 中标结果 河北</t>
+          <t>采购内容：AOI缺陷检测设备；公告类型：结果公告；发布时间：2026-09-02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>华润守正</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2499,39 +2499,39 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-439408833-4.html</t>
+          <t>https://www.szecp.com.cn/first_zbgg1/2026-07-21/2811085.html</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-09-03T12:10:52</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>重庆 芯联微电子 有限公司无图案晶圆缺陷检测设备中标结果公告(1)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片外观自动检测机采购项目成交候选人公示</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>晶圆缺陷检测设备中标结果公告(1)</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>检测设备，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆缺陷检测设备中标结果公告(1)；公告类型：结果公告；发布时间：2026-09-01</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片外观自动检测机采购项目成交候选人公示；可见摘要：3小时前 中标结果 河北</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -2544,12 +2544,12 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2561,39 +2561,39 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709735429.html</t>
+          <t>https://www.bidcenter.com.cn/news-439408833-4.html</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01T12:16:12</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>无锡中微腾芯电子有限公司全自动 集成电路 光学检验系统评标结果公示公告(1)</t>
+          <t>重庆 芯联微电子 有限公司无图案晶圆缺陷检测设备中标结果公告(1)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>待核验-设备功能不完整</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>无锡中微腾芯电子有限公司全自动 集成电路 光学检验系统评标结果公示公告(1)</t>
+          <t>晶圆缺陷检测设备中标结果公告(1)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
+          <t>检测设备，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>采购内容：无锡中微腾芯电子有限公司全自动 集成电路 光学检验系统评标结果公示公告(1)；公告类型：结果公示；发布时间：2026-09-01</t>
+          <t>采购内容：晶圆缺陷检测设备中标结果公告(1)；公告类型：结果公告；发布时间：2026-09-01</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>结果公示</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2623,39 +2623,39 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709739016.html</t>
+          <t>https://www.ebnew.com/businessShow/709735429.html</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T12:11:13</t>
+          <t>2026-09-01T12:16:12</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体湿法-1台晶圆盒清洗设备采购项目(全新设备)谈判采购结果公告</t>
+          <t>无锡中微腾芯电子有限公司全自动 集成电路 光学检验系统评标结果公示公告(1)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>待核验-设备功能不完整</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体湿法-1台晶圆盒清洗设备采购项目(全新设备)谈判采购</t>
+          <t>无锡中微腾芯电子有限公司全自动 集成电路 光学检验系统评标结果公示公告(1)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体湿法-1台晶圆盒清洗设备采购项目(全新设备)谈判采购；公告类型：结果公告；发布时间：2026-09-01</t>
+          <t>采购内容：无锡中微腾芯电子有限公司全自动 集成电路 光学检验系统评标结果公示公告(1)；公告类型：结果公示；发布时间：2026-09-01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2668,12 +2668,12 @@
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>华润守正</t>
+          <t>必联网</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>结果公示</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_jggg/2026-09-01/2808108.html</t>
+          <t>https://www.ebnew.com/businessShow/709739016.html</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -2697,27 +2697,27 @@
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>无锡华润微电子有限公司6AB、8B集中供液设备招标公告</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体湿法-1台晶圆盒清洗设备采购项目(全新设备)谈判采购结果公告</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>无锡华润微电子有限公司6AB、8B集中供液设备</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体湿法-1台晶圆盒清洗设备采购项目(全新设备)谈判采购</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告具有半导体产业链语境</t>
+          <t>TED，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>采购内容：无锡华润微电子有限公司6AB、8B集中供液设备；公告类型：招标公告；发布时间：2026-09-01</t>
+          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体湿法-1台晶圆盒清洗设备采购项目(全新设备)谈判采购；公告类型：结果公告；发布时间：2026-09-01</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2735,19 +2735,19 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_zbgg/2026-08-18/2807513.html</t>
+          <t>https://www.szecp.com.cn/first_jggg/2026-09-01/2808108.html</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -2759,43 +2759,47 @@
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购评标结...</t>
+          <t>无锡华润微电子有限公司6AB、8B集中供液设备招标公告</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学量测</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购评标结...</t>
+          <t>无锡华润微电子有限公司6AB、8B集中供液设备</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>成像，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>TED，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>采购内容：北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购评标结...；发布时间：2026-08-31</t>
+          <t>采购内容：无锡华润微电子有限公司6AB、8B集中供液设备；公告类型：招标公告；发布时间：2026-09-01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t>华润守正</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
           <t>进行中/未知</t>
@@ -2805,7 +2809,7 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709729634.html</t>
+          <t>https://www.szecp.com.cn/first_zbgg/2026-08-18/2807513.html</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -2817,69 +2821,65 @@
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目重新招标澄清或变更公告(1)-2435-264JT2026003</t>
+          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购评标结...</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学量测</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购评标结...</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>成像，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目重新招标澄清或变更公告(1)-2435-264JT2026003；可见摘要：2026-08-28 招标变更 河南</t>
+          <t>采购内容：北京大学重庆碳基集成电路研究院12寸碳基 晶圆 材料谱学与成像系统采购评标结...；发布时间：2026-08-31</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>招标变更</t>
-        </is>
-      </c>
+          <t>必联网</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-438897812-6.html</t>
+          <t>https://www.ebnew.com/businessShow/709729634.html</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-09-02T12:11:13</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>重庆芯联微电子有限公司无图案 晶圆 缺陷 检测 设备评标结果公示公告(1)-0613-264025124060</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目重新招标澄清或变更公告(1)-2435-264JT2026003</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：重庆芯联微电子有限公司无图案 晶圆 缺陷 检测 设备评标结果公示公告(1)-0613-264025124060；可见摘要：2026-08-28 中标结果 重庆</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目重新招标澄清或变更公告(1)-2435-264JT2026003；可见摘要：2026-08-28 招标变更 河南</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -2917,19 +2917,19 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-438922588-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-438897812-6.html</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司6A新购AOI 缺陷检测 设备中标候选人公示</t>
+          <t>重庆芯联微电子有限公司无图案 晶圆 缺陷 检测 设备评标结果公示公告(1)-0613-264025124060</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司6A新购AOI 缺陷检测 设备中标候选人公示；可见摘要：20小时前 中标结果 江苏</t>
+          <t>项目：重庆芯联微电子有限公司无图案 晶圆 缺陷 检测 设备评标结果公示公告(1)-0613-264025124060；可见摘要：2026-08-28 中标结果 重庆</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-438644711-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-438922588-4.html</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>zycgr220119022026年10至12月政府采购意向-芯片自动 光学检测 机详细情况120.000000万元(人民币)</t>
+          <t>无锡华润上华科技有限公司6A新购AOI 缺陷检测 设备中标候选人公示</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：zycgr220119022026年10至12月政府采购意向-芯片自动 光学检测 机详细情况120.000000万元(人民币)；可见摘要：18小时前 招标预告 跨省</t>
+          <t>项目：无锡华润上华科技有限公司6A新购AOI 缺陷检测 设备中标候选人公示；可见摘要：20小时前 中标结果 江苏</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -3041,19 +3041,19 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-438692986-2.html</t>
+          <t>https://www.bidcenter.com.cn/news-438644711-4.html</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -3065,27 +3065,27 @@
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目公告</t>
+          <t>zycgr220119022026年10至12月政府采购意向-芯片自动 光学检测 机详细情况120.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目；公告类型：采购公告；发布时间：2026-08-28</t>
+          <t>项目：zycgr220119022026年10至12月政府采购意向-芯片自动 光学检测 机详细情况120.000000万元(人民币)；可见摘要：18小时前 招标预告 跨省</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -3098,12 +3098,12 @@
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>华润守正</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3115,101 +3115,101 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_cggg/2026-08-27/2799757.html</t>
+          <t>https://www.bidcenter.com.cn/news-438692986-2.html</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T12:15:03</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目BMD 量测 设备采购项目中标结果公告(1)-1354-264HXZBG2603</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目公告</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>TED，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目BMD 量测 设备采购项目中标结果公告(1)-1354-264HXZBG2603；可见摘要：2026-08-25 中标结果 河南</t>
+          <t>采购内容：润鹏半导体(深圳)有限公司润鹏半导体90nm BCD平台1.5V SRAM TQV IP 采购项目；公告类型：采购公告；发布时间：2026-08-28</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>华润守正</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-438181039-4.html</t>
+          <t>https://www.szecp.com.cn/first_cggg/2026-08-27/2799757.html</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-08-28T12:15:03</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>中国检验认证集团江苏有限公司 半导体 工艺机台检验 检测 设备采购项目标段2：示踪气体 检测 仪（气相色谱仪）中标候选人公示（项目编号：JSTCC2500918267-2）</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目BMD 量测 设备采购项目中标结果公告(1)-1354-264HXZBG2603</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：中国检验认证集团江苏有限公司 半导体 工艺机台检验 检测 设备采购项目标段2：示踪气体 检测 仪（气相色谱仪）中标候选人公示（项目编号：JSTCC2500918267-2）；可见摘要：2026-08-25 中标结果 江苏</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目BMD 量测 设备采购项目中标结果公告(1)-1354-264HXZBG2603；可见摘要：2026-08-25 中标结果 河南</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3239,7 +3239,7 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-438206007-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-438181039-4.html</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -3251,27 +3251,27 @@
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目BM...</t>
+          <t>中国检验认证集团江苏有限公司 半导体 工艺机台检验 检测 设备采购项目标段2：示踪气体 检测 仪（气相色谱仪）中标候选人公示（项目编号：JSTCC2500918267-2）</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>待核验-设备功能不完整</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目BM...</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>采购内容：麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目BM...；发布时间：2026-08-25</t>
+          <t>项目：中国检验认证集团江苏有限公司 半导体 工艺机台检验 检测 设备采购项目标段2：示踪气体 检测 仪（气相色谱仪）中标候选人公示（项目编号：JSTCC2500918267-2）；可见摘要：2026-08-25 中标结果 江苏</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -3284,94 +3284,94 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709648865.html</t>
+          <t>https://www.bidcenter.com.cn/news-438206007-4.html</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T12:12:04</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台重新招标澄清或变更公告(1)-0692-2640XM075270/04</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目BM...</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>待核验-设备功能不完整</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目BM...</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台重新招标澄清或变更公告(1)-0692-2640XM075270/04；可见摘要：2026-08-24 招标变更 江苏</t>
+          <t>采购内容：麦斯克电子材料（郑州）有限公司年产360万片8英寸半导体特色硅抛光片项目BM...；发布时间：2026-08-25</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>招标变更</t>
-        </is>
-      </c>
+          <t>必联网</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-437939108-6.html</t>
+          <t>https://www.ebnew.com/businessShow/709648865.html</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-08-26T12:12:04</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台重新招标澄清或变更公告(1)-0692-2640XM075270/01</t>
+          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台重新招标澄清或变更公告(1)-0692-2640XM075270/04</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台重新招标澄清或变更公告(1)-0692-2640XM075270/01；可见摘要：2026-08-24 招标变更 江苏</t>
+          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台重新招标澄清或变更公告(1)-0692-2640XM075270/04；可见摘要：2026-08-24 招标变更 江苏</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-437939098-6.html</t>
+          <t>https://www.bidcenter.com.cn/news-437939108-6.html</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>半导体 温控 检测 系统竞价结果（202610109106）</t>
+          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台重新招标澄清或变更公告(1)-0692-2640XM075270/01</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：半导体 温控 检测 系统竞价结果（202610109106）；可见摘要：2026-08-24 中标结果 广东</t>
+          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台重新招标澄清或变更公告(1)-0692-2640XM075270/01；可见摘要：2026-08-24 招标变更 江苏</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3471,19 +3471,19 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-437973507-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-437939098-6.html</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -3495,89 +3495,89 @@
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)</t>
+          <t>半导体 温控 检测 系统竞价结果（202610109106）</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>待核验-设备功能不完整</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) [招标公告] 上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) 发布时间：2026-08-21 上海机电设备招标有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**在中... 信息属性 所属行业： 量仪 所属地区： 上海市 资金来源： 现汇项目</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>采购内容：上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) [招标公告] 上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) 发布时间：2026-08-21 上海机电设备招标有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**在中... 信息属性 所属行业： 量仪 所属地区： 上海市 资金来源： 现汇项目；公告类型：招标公告；发布时间：2026-08-21</t>
+          <t>项目：半导体 温控 检测 系统竞价结果（202610109106）；可见摘要：2026-08-24 中标结果 广东</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>机电产品招标投标电子交易平台</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.chinabidding.com/bidDetail/263288502.html</t>
+          <t>https://www.bidcenter.com.cn/news-437973507-4.html</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22T12:14:17</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司 颗粒检测 设备采购中标结果公告(1)</t>
+          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>待核验-缺少晶圆/衬底场景</t>
+          <t>待核验-设备功能不完整</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司 颗粒检测 设备采购中标结果公告(1)</t>
+          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) [招标公告] 上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) 发布时间：2026-08-21 上海机电设备招标有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**在中... 信息属性 所属行业： 量仪 所属地区： 上海市 资金来源： 现汇项目</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>看到颗粒检测，但未看到晶圆/硅片/SiC/衬底场景</t>
+          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>采购内容：陕西电子芯业时代科技有限公司 颗粒检测 设备采购中标结果公告(1)；公告类型：结果公告；发布时间：2026-08-21</t>
+          <t>采购内容：上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) [招标公告] 上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1) 发布时间：2026-08-21 上海机电设备招标有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**在中... 信息属性 所属行业： 量仪 所属地区： 上海市 资金来源： 现汇项目；公告类型：招标公告；发布时间：2026-08-21</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3590,24 +3590,24 @@
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
+          <t>机电产品招标投标电子交易平台</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709600174.html</t>
+          <t>https://www.chinabidding.com/bidDetail/263288502.html</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -3619,27 +3619,27 @@
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)</t>
+          <t>陕西电子芯业时代科技有限公司 颗粒检测 设备采购中标结果公告(1)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>待核验-设备功能不完整</t>
+          <t>待核验-缺少晶圆/衬底场景</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)</t>
+          <t>陕西电子芯业时代科技有限公司 颗粒检测 设备采购中标结果公告(1)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
+          <t>看到颗粒检测，但未看到晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>采购内容：上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-21</t>
+          <t>采购内容：陕西电子芯业时代科技有限公司 颗粒检测 设备采购中标结果公告(1)；公告类型：结果公告；发布时间：2026-08-21</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3657,19 +3657,19 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709598075.html</t>
+          <t>https://www.ebnew.com/businessShow/709600174.html</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -3681,40 +3681,40 @@
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目国际招标公告（1）</t>
+          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>待核验-设备功能不完整</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>仅看到半导体语境，未看到目标检测/量测设备功能</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目国际招标公告（1）；可见摘要：2026-08-20 招标公告 河南</t>
+          <t>采购内容：上海易启芯程 半导体 有限公司非接触式测量设备国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-21</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>必联网</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3731,46 +3731,42 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-437382421-1.html</t>
+          <t>https://www.ebnew.com/businessShow/709598075.html</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-08-22T12:14:17</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>光刻版检测设备【重新招标】-公开招标公告</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目国际招标公告（1）</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>待核验-缺少晶圆/衬底场景</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>1. 招标条件 本招标项目光刻版检测设备，招标人为中国电子科技集团公司第五十八研究所 ，招标项目资金 来 自 国拨资金 ， 出 资 比 例为 100%</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>看到检测设备，但未看到晶圆/硅片/SiC/衬底场景</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>采购内容：1. 招标条件 本招标项目光刻版检测设备，招标人为中国电子科技集团公司第五十八研究所 ，招标项目资金 来 自 国拨资金 ， 出 资 比 例为 100%；数量：1台；采购方：中国电子科技集团公司第五十八研究所；公告类型：公开招标公告；发布时间：2026-08-20</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>中国电子科技集团公司第五十八研究所</t>
-        </is>
-      </c>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目最终 检测 设备采购项目国际招标公告（1）；可见摘要：2026-08-20 招标公告 河南</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3780,12 +3776,12 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -3797,19 +3793,19 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/860254.jhtml</t>
+          <t>https://www.bidcenter.com.cn/news-437382421-1.html</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T12:07:43</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8吋 膜厚 仪采购项目（二次）中标结果公告(1)</t>
+          <t>光刻版检测设备【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3819,159 +3815,163 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8吋 膜厚 仪采购项目（二次）中标结果公告(1)</t>
+          <t>1. 招标条件 本招标项目光刻版检测设备，招标人为中国电子科技集团公司第五十八研究所 ，招标项目资金 来 自 国拨资金 ， 出 资 比 例为 100%</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>看到膜厚，但未看到晶圆/硅片/SiC/衬底场景</t>
+          <t>看到检测设备，但未看到晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>采购内容：陕西电子芯业时代科技有限公司8吋 膜厚 仪采购项目（二次）中标结果公告(1)；公告类型：结果公告；发布时间：2026-08-19</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
+          <t>采购内容：1. 招标条件 本招标项目光刻版检测设备，招标人为中国电子科技集团公司第五十八研究所 ，招标项目资金 来 自 国拨资金 ， 出 资 比 例为 100%；数量：1台；采购方：中国电子科技集团公司第五十八研究所；公告类型：公开招标公告；发布时间：2026-08-20</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>中国电子科技集团公司第五十八研究所</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709566442.html</t>
+          <t>https://www.365trade.com.cn/zhwzb/860254.jhtml</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T12:08:42</t>
+          <t>2026-08-21T12:07:43</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>润西微电子(重庆)有限公司润西二期扩容特气设备采购公告</t>
+          <t>陕西电子芯业时代科技有限公司8吋 膜厚 仪采购项目（二次）中标结果公告(1)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>待核验-缺少晶圆/衬底场景</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>润西微电子(重庆)有限公司润西二期扩容特气设备</t>
+          <t>陕西电子芯业时代科技有限公司8吋 膜厚 仪采购项目（二次）中标结果公告(1)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告具有半导体产业链语境</t>
+          <t>看到膜厚，但未看到晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>采购内容：润西微电子(重庆)有限公司润西二期扩容特气设备；公告类型：采购公告；发布时间：2026-08-18</t>
+          <t>采购内容：陕西电子芯业时代科技有限公司8吋 膜厚 仪采购项目（二次）中标结果公告(1)；公告类型：结果公告；发布时间：2026-08-19</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>华润守正</t>
+          <t>必联网</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_cggg/2026-08-18/2777594.html</t>
+          <t>https://www.ebnew.com/businessShow/709566442.html</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19T12:05:08</t>
+          <t>2026-08-20T12:08:42</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>晶圆 表面形貌 量测设备国际招标公告(1)-0664-2640SUMECF93</t>
+          <t>润西微电子(重庆)有限公司润西二期扩容特气设备采购公告</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>形貌量测</t>
+          <t>润西微电子(重庆)有限公司润西二期扩容特气设备</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>形貌量测 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>TED，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆 表面形貌 量测设备国际招标公告(1)-0664-2640SUMECF93；可见摘要：2026-08-17 招标公告 浙江</t>
+          <t>采购内容：润西微电子(重庆)有限公司润西二期扩容特气设备；公告类型：采购公告；发布时间：2026-08-18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>华润守正</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -3983,39 +3983,39 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436609726-1.html</t>
+          <t>https://www.szecp.com.cn/first_cggg/2026-08-18/2777594.html</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-08-19T12:05:08</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面形貌 量测 设备国际招标公告(1)</t>
+          <t>晶圆 表面形貌 量测设备国际招标公告(1)-0664-2640SUMECF93</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学量测</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面形貌 量测 设备国际招标公告(1)</t>
+          <t>形貌量测</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>量测，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>形貌量测 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆表面形貌 量测 设备国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-17</t>
+          <t>项目：晶圆 表面形貌 量测设备国际招标公告(1)-0664-2640SUMECF93；可见摘要：2026-08-17 招标公告 浙江</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -4028,7 +4028,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>机电产品招标投标电子交易平台</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.chinabidding.com/bidDetail/263271970.html</t>
+          <t>https://www.bidcenter.com.cn/news-436609726-1.html</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T12:11:09</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
+          <t>机电产品招标投标电子交易平台</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709536968.html</t>
+          <t>https://www.chinabidding.com/bidDetail/263271970.html</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -4119,27 +4119,27 @@
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>无锡华润微电子有限公司微电子中央研究院高低温高压大电流模块动态特性测试设备谈判采购公告</t>
+          <t>晶圆表面形貌 量测 设备国际招标公告(1)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>晶圆/衬底光学量测</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>无锡华润微电子有限公司微电子中央研究院高低温高压大电流模块动态特性测试设备谈判</t>
+          <t>晶圆表面形貌 量测 设备国际招标公告(1)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告具有半导体产业链语境</t>
+          <t>量测，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>采购内容：无锡华润微电子有限公司微电子中央研究院高低温高压大电流模块动态特性测试设备谈判；公告类型：采购公告；发布时间：2026-08-17</t>
+          <t>采购内容：晶圆表面形貌 量测 设备国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-17</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -4152,12 +4152,12 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>华润守正</t>
+          <t>必联网</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -4169,39 +4169,39 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_cggg/2026-08-17/2775752.html</t>
+          <t>https://www.ebnew.com/businessShow/709536968.html</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T12:09:34</t>
+          <t>2026-08-17T12:11:09</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>无锡华润安盛科技有限公司安盛自动AOI检测设备公告</t>
+          <t>无锡华润微电子有限公司微电子中央研究院高低温高压大电流模块动态特性测试设备谈判采购公告</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>待核验-采购对象不明确</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>AOI检测设备</t>
+          <t>无锡华润微电子有限公司微电子中央研究院高低温高压大电流模块动态特性测试设备谈判</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>看到检测设备，但未确认采购对象为设备/系统/仪器</t>
+          <t>TED，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>采购内容：AOI检测设备；公告类型：采购公告；发布时间：2026-08-17</t>
+          <t>采购内容：无锡华润微电子有限公司微电子中央研究院高低温高压大电流模块动态特性测试设备谈判；公告类型：采购公告；发布时间：2026-08-17</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -4231,46 +4231,46 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_cggg/2026-08-17/2774846.html</t>
+          <t>https://www.szecp.com.cn/first_cggg/2026-08-17/2775752.html</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T12:08:42</t>
+          <t>2026-08-18T12:09:34</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司1台前段等离子氧化沉积设备采购谈判采购结果公告</t>
+          <t>无锡华润安盛科技有限公司安盛自动AOI检测设备公告</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>待核验-采购对象不明确</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>润鹏半导体(深圳)有限公司1台前段等离子氧化沉积设备采购谈判采购</t>
+          <t>AOI检测设备</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>TED，且公告具有半导体产业链语境</t>
+          <t>看到检测设备，但未确认采购对象为设备/系统/仪器</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>采购内容：润鹏半导体(深圳)有限公司1台前段等离子氧化沉积设备采购谈判采购；公告类型：结果公告；发布时间：2026-08-16</t>
+          <t>采购内容：AOI检测设备；公告类型：采购公告；发布时间：2026-08-17</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -4281,69 +4281,69 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.szecp.com.cn/first_jggg/2026-07-21/2772901.html</t>
+          <t>https://www.szecp.com.cn/first_cggg/2026-08-17/2774846.html</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16T12:19:24</t>
+          <t>2026-08-20T12:08:42</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司晶圆 缺陷检测 仪等设备采购项目（二包）中标通知书</t>
+          <t>润鹏半导体(深圳)有限公司1台前段等离子氧化沉积设备采购谈判采购结果公告</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>润鹏半导体(深圳)有限公司1台前段等离子氧化沉积设备采购谈判采购</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>TED，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司晶圆 缺陷检测 仪等设备采购项目（二包）中标通知书；可见摘要：20小时前 中标结果 安徽</t>
+          <t>采购内容：润鹏半导体(深圳)有限公司1台前段等离子氧化沉积设备采购谈判采购；公告类型：结果公告；发布时间：2026-08-16</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>华润守正</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -4355,19 +4355,19 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436131155-4.html</t>
+          <t>https://www.szecp.com.cn/first_jggg/2026-07-21/2772901.html</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-08-16T12:19:24</t>
         </is>
       </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>株洲中车时代半导体股份有限公司 AOI 检测设备采购项目招标公告</t>
+          <t>芜湖智能传感器研究院有限公司晶圆 缺陷检测 仪等设备采购项目（二包）中标通知书</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>项目：株洲中车时代半导体股份有限公司 AOI 检测设备采购项目招标公告；可见摘要：2026-08-14 招标公告 湖南</t>
+          <t>项目：芜湖智能传感器研究院有限公司晶圆 缺陷检测 仪等设备采购项目（二包）中标通知书；可见摘要：20小时前 中标结果 安徽</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -4405,19 +4405,19 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436383461-1.html</t>
+          <t>https://www.bidcenter.com.cn/news-436131155-4.html</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台国际招标公告(1)</t>
+          <t>株洲中车时代半导体股份有限公司 AOI 检测设备采购项目招标公告</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4439,17 +4439,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台国际招标公告(1)；可见摘要：2026-08-14 招标公告 广东</t>
+          <t>项目：株洲中车时代半导体股份有限公司 AOI 检测设备采购项目招标公告；可见摘要：2026-08-14 招标公告 湖南</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -4479,7 +4479,7 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436412236-1.html</t>
+          <t>https://www.bidcenter.com.cn/news-436383461-1.html</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台国际招标公告(1)</t>
+          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台国际招标公告(1)</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台国际招标公告(1)；可见摘要：2026-08-14 招标公告 广东</t>
+          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机（盲孔）1台国际招标公告(1)；可见摘要：2026-08-14 招标公告 广东</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -4541,7 +4541,7 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436412234-1.html</t>
+          <t>https://www.bidcenter.com.cn/news-436412236-1.html</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -4553,35 +4553,31 @@
     <row r="66" ht="58" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>全自动晶圆隐切设备重新招标澄清或变更公告1</t>
+          <t>南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台国际招标公告(1)</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>项目：全自动晶圆隐切设备重新招标澄清或变更公告1；中标/候选人：潜在中标人 根据类似；可见摘要：11小时前 招标变更 上海</t>
+          <t>项目：南通康源集成电路封装载板项目（一期）-自动 光学检测 机2台国际招标公告(1)；可见摘要：2026-08-14 招标公告 广东</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>潜在中标人 根据类似</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
@@ -4595,19 +4591,19 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436188391-6.html</t>
+          <t>https://www.bidcenter.com.cn/news-436412234-1.html</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -4619,31 +4615,35 @@
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机（1um）国际招标公告(1)</t>
+          <t>全自动晶圆隐切设备重新招标澄清或变更公告1</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查AOI</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机（1um）国际招标公告(1)</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>设备名称明确为自动光学检查机，精度/线上特征符合工业缺陷检测。</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>采购内容：自动光学检查机（1um）国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-14</t>
+          <t>项目：全自动晶圆隐切设备重新招标澄清或变更公告1；中标/候选人：潜在中标人 根据类似；可见摘要：11小时前 招标变更 上海</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>潜在中标人 根据类似</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
@@ -4652,56 +4652,56 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709500330.html</t>
+          <t>https://www.bidcenter.com.cn/news-436188391-6.html</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:00:05</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="68" ht="58" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>线宽 量测 机中标结果公告(1)</t>
+          <t>自动光学检查机（1um）国际招标公告(1)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>待核验-缺少晶圆/衬底场景</t>
+          <t>自动光学检查AOI</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>线宽 量测 机中标结果公告(1)</t>
+          <t>自动光学检查机（1um）国际招标公告(1)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>看到量测，但未看到晶圆/硅片/SiC/衬底场景</t>
+          <t>设备名称明确为自动光学检查机，精度/线上特征符合工业缺陷检测。</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>采购内容：线宽 量测 机中标结果公告(1)；公告类型：结果公告；发布时间：2026-08-14</t>
+          <t>采购内容：自动光学检查机（1um）国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-14</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -4719,51 +4719,51 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709506637.html</t>
+          <t>https://www.ebnew.com/businessShow/709500330.html</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T12:10:49</t>
+          <t>2026-08-14T11:00:05</t>
         </is>
       </c>
     </row>
     <row r="69" ht="58" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>线上自动光学检查机国际招标公告(1)</t>
+          <t>线宽 量测 机中标结果公告(1)</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查AOI</t>
+          <t>待核验-缺少晶圆/衬底场景</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>线上自动光学检查机国际招标公告(1)</t>
+          <t>线宽 量测 机中标结果公告(1)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>设备名称明确为自动光学检查机，精度/线上特征符合工业缺陷检测。</t>
+          <t>看到量测，但未看到晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>采购内容：线上自动光学检查机国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-14</t>
+          <t>采购内容：线宽 量测 机中标结果公告(1)；公告类型：结果公告；发布时间：2026-08-14</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -4781,51 +4781,51 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709500463.html</t>
+          <t>https://www.ebnew.com/businessShow/709506637.html</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:00:05</t>
+          <t>2026-08-15T12:10:49</t>
         </is>
       </c>
     </row>
     <row r="70" ht="58" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>深圳职业技术大学中低功率半导体电学 量测 设备（A）招标公告</t>
+          <t>线上自动光学检查机国际招标公告(1)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>自动光学检查AOI</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>深圳职业技术大学中低功率半导体电学 量测 设备（A）</t>
+          <t>线上自动光学检查机国际招标公告(1)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>量测，且公告具有半导体产业链语境</t>
+          <t>设备名称明确为自动光学检查机，精度/线上特征符合工业缺陷检测。</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>采购内容：深圳职业技术大学中低功率半导体电学 量测 设备（A）；公告类型：招标公告；发布时间：2026-08-14</t>
+          <t>采购内容：线上自动光学检查机国际招标公告(1)；公告类型：招标公告；发布时间：2026-08-14</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4855,81 +4855,81 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709505766.html</t>
+          <t>https://www.ebnew.com/businessShow/709500463.html</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15T12:10:49</t>
+          <t>2026-08-14T11:00:05</t>
         </is>
       </c>
     </row>
     <row r="71" ht="58" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS 检测 设备采购项目重新招标澄清或变更公告(1) 附件</t>
+          <t>深圳职业技术大学中低功率半导体电学 量测 设备（A）招标公告</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>深圳职业技术大学中低功率半导体电学 量测 设备（A）</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS 检测 设备采购项目重新招标澄清或变更公告(1) 附件；可见摘要：2026-08-13 招标变更 河南</t>
+          <t>采购内容：深圳职业技术大学中低功率半导体电学 量测 设备（A）；公告类型：招标公告；发布时间：2026-08-14</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>必联网</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436201340-6.html</t>
+          <t>https://www.ebnew.com/businessShow/709505766.html</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13T12:07:13</t>
+          <t>2026-08-15T12:10:49</t>
         </is>
       </c>
     </row>
     <row r="72" ht="58" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学 半导体 微纳传感器件参数 检测 仪招标公告 附件</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS 检测 设备采购项目重新招标澄清或变更公告(1) 附件</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学 半导体 微纳传感器件参数 检测 仪招标公告 附件；可见摘要：22小时前 招标公告 陕西</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS 检测 设备采购项目重新招标澄清或变更公告(1) 附件；可见摘要：2026-08-13 招标变更 河南</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4967,19 +4967,19 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-435941152-1.html</t>
+          <t>https://www.bidcenter.com.cn/news-436201340-6.html</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
     <row r="73" ht="58" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>晶圆缺陷检测仪等设备采购项目二包中标结果公告</t>
+          <t>西安理工大学 半导体 微纳传感器件参数 检测 仪招标公告 附件</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -5001,25 +5001,21 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆缺陷检测仪等设备采购项目二包中标结果公告；中标/候选人：南京 (略) 供应商；可见摘要：3分钟前 中标结果 安徽</t>
+          <t>项目：西安理工大学 半导体 微纳传感器件参数 检测 仪招标公告 附件；可见摘要：22小时前 招标公告 陕西</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>南京 (略) 供应商</t>
-        </is>
-      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
@@ -5033,19 +5029,19 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436131154-4.html</t>
+          <t>https://www.bidcenter.com.cn/news-435941152-1.html</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -5057,31 +5053,35 @@
     <row r="74" ht="58" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司全自动晶圆 量测 设备重新招标澄清或变更公告(1) 附件</t>
+          <t>晶圆缺陷检测仪等设备采购项目二包中标结果公告</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司全自动晶圆 量测 设备重新招标澄清或变更公告(1) 附件；可见摘要：2026-08-13 招标变更 上海</t>
+          <t>项目：晶圆缺陷检测仪等设备采购项目二包中标结果公告；中标/候选人：南京 (略) 供应商；可见摘要：3分钟前 中标结果 安徽</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>南京 (略) 供应商</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
@@ -5095,19 +5095,19 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-436188194-6.html</t>
+          <t>https://www.bidcenter.com.cn/news-436131154-4.html</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -5119,34 +5119,34 @@
     <row r="75" ht="58" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>气化事业部-气化事业部-中科飞测 集成电路 检测 设备装备上海张江研发中心及生产基地洁净机电工程-容器设备项目公告</t>
+          <t>上海易启芯程 半导体 有限公司全自动晶圆 量测 设备重新招标澄清或变更公告(1) 附件</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>项目：气化事业部-气化事业部-中科飞测 集成电路 检测 设备装备上海张江研发中心及生产基地洁净机电工程-容器设备项目公告；可见摘要：收藏 招标公告 上海 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司全自动晶圆 量测 设备重新招标澄清或变更公告(1) 附件；可见摘要：2026-08-13 招标变更 上海</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -5157,19 +5157,19 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-435564059</t>
+          <t>https://www.bidcenter.com.cn/news-436188194-6.html</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -5181,27 +5181,27 @@
     <row r="76" ht="58" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>无锡 华润上华 科技有限公司CD-SEM图像品质提升公告</t>
+          <t>气化事业部-气化事业部-中科飞测 集成电路 检测 设备装备上海张江研发中心及生产基地洁净机电工程-容器设备项目公告</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡 华润上华 科技有限公司CD-SEM图像品质提升公告；可见摘要：2026-08-12 招标公告 江苏</t>
+          <t>项目：气化事业部-气化事业部-中科飞测 集成电路 检测 设备装备上海张江研发中心及生产基地洁净机电工程-容器设备项目公告；可见摘要：收藏 招标公告 上海 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -5231,7 +5231,7 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/news-435754223-1.html</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-435564059</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -5243,27 +5243,27 @@
     <row r="77" ht="58" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标失败公告</t>
+          <t>无锡 华润上华 科技有限公司CD-SEM图像品质提升公告</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标失败公告；可见摘要：附件 收藏 招标变更 安徽 21小时前；详情状态：受限，需人工核验</t>
+          <t>项目：无锡 华润上华 科技有限公司CD-SEM图像品质提升公告；可见摘要：2026-08-12 招标公告 江苏</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-435538238</t>
+          <t>https://www.bidcenter.com.cn/news-435754223-1.html</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="78" ht="58" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购中标公示</t>
+          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标失败公告</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5315,17 +5315,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>掩模缺陷检测仪</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购中标公示；可见摘要：收藏 中标结果 广东 19小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标失败公告；可见摘要：附件 收藏 招标变更 安徽 21小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -5343,19 +5343,19 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-435561654</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-435538238</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -5367,27 +5367,27 @@
     <row r="79" ht="58" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ADC自动 缺陷检测 系统 国际招标公告(2)</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购中标公示</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>半导体缺陷检测/ADC</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ADC自动缺陷检测系统；原始摘要：ADC自动 缺陷检测 系统 国际招标公告(2) [招标公告] ADC自动 缺陷检测 系统 国际招标公告(2) 发布时间：2026-08-12 中航招采科技（北京）有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**... 信息属性 所属行业： 其它仪器仪表 所属地区： 安徽省 资金来源： 现汇项目</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>标题或采购内容明确指向ADC自动缺陷检测系统，属于半导体光学缺陷检测或晶圆关键量测方向。</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>采购内容：ADC自动 缺陷检测 系统 国际招标公告(2) [招标公告] ADC自动 缺陷检测 系统 国际招标公告(2) 发布时间：2026-08-12 中航招采科技（北京）有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**... 信息属性 所属行业： 其它仪器仪表 所属地区： 安徽省 资金来源： 现汇项目；公告类型：招标公告；发布时间：2026-08-12</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购中标公示；可见摘要：收藏 中标结果 广东 19小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -5400,36 +5400,36 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>机电产品招标投标电子交易平台</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>https://www.chinabidding.com/bidDetail/263258152.html</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-435561654</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T17:34:16</t>
+          <t>2026-09-13T12:07:13</t>
         </is>
       </c>
     </row>
     <row r="80" ht="58" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ADC 自动缺陷检测系统 重新招标澄清或变更公告(1)</t>
+          <t>ADC自动 缺陷检测 系统 国际招标公告(2)</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ADC自动缺陷检测系统；原始摘要：ADC 自动缺陷检测系统 重新招标澄清或变更公告(1)</t>
+          <t>ADC自动缺陷检测系统；原始摘要：ADC自动 缺陷检测 系统 国际招标公告(2) [招标公告] ADC自动 缺陷检测 系统 国际招标公告(2) 发布时间：2026-08-12 中航招采科技（北京）有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**... 信息属性 所属行业： 其它仪器仪表 所属地区： 安徽省 资金来源： 现汇项目</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>采购内容：ADC 自动缺陷检测系统 重新招标澄清或变更公告(1)；公告类型：变更公告；发布时间：2026-08-12</t>
+          <t>采购内容：ADC自动 缺陷检测 系统 国际招标公告(2) [招标公告] ADC自动 缺陷检测 系统 国际招标公告(2) 发布时间：2026-08-12 中航招采科技（北京）有限公司受招标人委托对下列产品及服务进行国际公开竞争性招标，于****-**-**... 信息属性 所属行业： 其它仪器仪表 所属地区： 安徽省 资金来源： 现汇项目；公告类型：招标公告；发布时间：2026-08-12</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -5462,24 +5462,24 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>必联网</t>
+          <t>机电产品招标投标电子交易平台</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>变更公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709471007.html</t>
+          <t>https://www.chinabidding.com/bidDetail/263258152.html</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="81" ht="58" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ADC 自动缺陷检测系统 国际招标公告(2)</t>
+          <t>ADC 自动缺陷检测系统 重新招标澄清或变更公告(1)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ADC自动缺陷检测系统；原始摘要：ADC 自动缺陷检测系统 国际招标公告(2)</t>
+          <t>ADC自动缺陷检测系统；原始摘要：ADC 自动缺陷检测系统 重新招标澄清或变更公告(1)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>采购内容：ADC 自动缺陷检测系统 国际招标公告(2)；公告类型：招标公告；发布时间：2026-08-12</t>
+          <t>采购内容：ADC 自动缺陷检测系统 重新招标澄清或变更公告(1)；公告类型：变更公告；发布时间：2026-08-12</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -5529,19 +5529,19 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>变更公告</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebnew.com/businessShow/709471326.html</t>
+          <t>https://www.ebnew.com/businessShow/709471007.html</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-13T12:11:19</t>
+          <t>2026-09-13T15:26:33</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -1086,7 +1086,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13848,7 +13848,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14220,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14344,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14720,7 +14720,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14844,7 +14844,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:06:38</t>
+          <t>2026-09-20T12:06:36</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19T12:10:53</t>
+          <t>2026-09-20T12:20:38</t>
         </is>
       </c>
     </row>
